--- a/data/trans_dic/P16A10-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,13</t>
+          <t>10,34; 14,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 15,17</t>
+          <t>10,85; 15,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 15,05</t>
+          <t>10,67; 15,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 18,11</t>
+          <t>12,6; 17,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 12,65</t>
+          <t>9,18; 12,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 12,48</t>
+          <t>9,2; 12,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 15,07</t>
+          <t>10,47; 14,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 17,58</t>
+          <t>13,9; 17,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,93</t>
+          <t>10,25; 12,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 13,12</t>
+          <t>10,45; 13,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,3</t>
+          <t>11,14; 14,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,97; 17,21</t>
+          <t>14,07; 17,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,2</t>
+          <t>1,66; 3,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,19</t>
+          <t>1,69; 3,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,27</t>
+          <t>3,51; 5,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,55</t>
+          <t>2,46; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,46</t>
+          <t>1,11; 2,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,96</t>
+          <t>0,86; 2,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,3</t>
+          <t>1,78; 3,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,81</t>
+          <t>1,53; 2,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,54</t>
+          <t>1,58; 2,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,42</t>
+          <t>1,45; 2,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,02</t>
+          <t>2,87; 3,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,47</t>
+          <t>2,2; 3,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,75</t>
+          <t>1,09; 3,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,44</t>
+          <t>0,83; 3,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,11</t>
+          <t>1,84; 5,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,32</t>
+          <t>2,77; 5,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,26</t>
+          <t>0,78; 3,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,42</t>
+          <t>1,55; 4,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,08</t>
+          <t>1,21; 2,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,99</t>
+          <t>1,12; 2,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,26</t>
+          <t>0,63; 2,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,23</t>
+          <t>1,93; 4,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,74</t>
+          <t>2,2; 3,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,27</t>
+          <t>4,69; 6,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,12</t>
+          <t>4,57; 6,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,95</t>
+          <t>5,23; 6,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,21</t>
+          <t>4,0; 6,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,04</t>
+          <t>4,57; 6,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,56</t>
+          <t>4,13; 5,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,18</t>
+          <t>4,56; 6,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,61</t>
+          <t>4,01; 5,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,88</t>
+          <t>4,84; 5,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 5,64</t>
+          <t>4,51; 5,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,26</t>
+          <t>5,08; 6,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,75</t>
+          <t>4,41; 5,71</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106143; 145784</t>
+          <t>106651; 147643</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104583; 147557</t>
+          <t>105532; 147470</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82434; 113547</t>
+          <t>80455; 115657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65460; 93050</t>
+          <t>64752; 91070</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>121239; 166423</t>
+          <t>120727; 167906</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>121764; 166325</t>
+          <t>122600; 168402</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>103953; 149903</t>
+          <t>104163; 148881</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>105030; 132087</t>
+          <t>104420; 133261</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>240225; 303353</t>
+          <t>240609; 302019</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>237987; 302388</t>
+          <t>240791; 302872</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189651; 250067</t>
+          <t>194785; 252541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>176759; 217728</t>
+          <t>178091; 217600</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29229; 54206</t>
+          <t>28066; 52579</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34131; 62512</t>
+          <t>33097; 60305</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70899; 109438</t>
+          <t>72787; 108290</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57328; 104286</t>
+          <t>56437; 104717</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18293; 39039</t>
+          <t>17673; 39150</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14038; 34419</t>
+          <t>15024; 35161</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35495; 65558</t>
+          <t>35326; 65387</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33905; 62865</t>
+          <t>34167; 62431</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50917; 83443</t>
+          <t>51774; 83744</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53461; 89878</t>
+          <t>53820; 88510</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115474; 163287</t>
+          <t>116520; 161571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>104027; 157276</t>
+          <t>99418; 154767</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5509; 20676</t>
+          <t>6014; 20110</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3774; 16536</t>
+          <t>4010; 17259</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9994; 27933</t>
+          <t>10043; 29278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17985; 34399</t>
+          <t>17887; 34419</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3528; 15546</t>
+          <t>3734; 15936</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7879</t>
+          <t>0; 7421</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8360; 24294</t>
+          <t>8523; 25240</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8082; 20312</t>
+          <t>8003; 19299</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11474; 30758</t>
+          <t>11557; 30269</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5346; 21211</t>
+          <t>5945; 21397</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21926; 46369</t>
+          <t>21196; 45925</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28966; 48875</t>
+          <t>28817; 49712</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>151478; 205422</t>
+          <t>153538; 202598</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>156288; 208910</t>
+          <t>155833; 211960</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177683; 234719</t>
+          <t>176755; 230791</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>144269; 214283</t>
+          <t>138207; 213386</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>154492; 204222</t>
+          <t>154493; 207824</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>145424; 197266</t>
+          <t>146360; 195298</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>160922; 218296</t>
+          <t>161238; 219881</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>149276; 204620</t>
+          <t>146409; 205395</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>319374; 391562</t>
+          <t>322063; 393925</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>316041; 392097</t>
+          <t>313504; 386567</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>350968; 432557</t>
+          <t>351132; 433055</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>319534; 408345</t>
+          <t>313296; 405725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A10-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 14,31</t>
+          <t>10,24; 14,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 15,16</t>
+          <t>10,67; 15,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,33</t>
+          <t>10,8; 15,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 17,72</t>
+          <t>12,15; 17,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,77</t>
+          <t>9,34; 12,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,64</t>
+          <t>9,15; 12,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 14,97</t>
+          <t>10,48; 14,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 17,73</t>
+          <t>13,88; 17,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 12,87</t>
+          <t>10,35; 12,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 13,14</t>
+          <t>10,44; 13,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 14,44</t>
+          <t>11,27; 14,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 17,2</t>
+          <t>13,78; 16,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,11</t>
+          <t>1,76; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,08</t>
+          <t>1,73; 3,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,22</t>
+          <t>3,39; 5,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,57</t>
+          <t>3,38; 4,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,47</t>
+          <t>1,1; 2,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,0</t>
+          <t>0,84; 2,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,29</t>
+          <t>1,82; 3,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,79</t>
+          <t>2,02; 3,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,55</t>
+          <t>1,59; 2,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,38</t>
+          <t>1,47; 2,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,97</t>
+          <t>2,85; 4,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,42</t>
+          <t>2,8; 3,82</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,65</t>
+          <t>0,99; 3,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,59</t>
+          <t>0,84; 3,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,35</t>
+          <t>1,8; 5,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,32</t>
+          <t>3,03; 5,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,35</t>
+          <t>0,73; 3,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,6</t>
+          <t>1,54; 4,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,92</t>
+          <t>1,33; 2,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,95</t>
+          <t>1,07; 2,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,28</t>
+          <t>0,57; 2,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,19</t>
+          <t>2,02; 4,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,8</t>
+          <t>2,36; 3,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,19</t>
+          <t>4,7; 6,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,21</t>
+          <t>4,5; 6,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,83</t>
+          <t>5,17; 6,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,18</t>
+          <t>5,1; 6,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,15</t>
+          <t>4,6; 6,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,51</t>
+          <t>4,11; 5,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,23</t>
+          <t>4,62; 6,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,63</t>
+          <t>4,79; 5,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,92</t>
+          <t>4,8; 5,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 5,56</t>
+          <t>4,52; 5,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,27</t>
+          <t>5,1; 6,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 5,71</t>
+          <t>5,12; 6,04</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78207</t>
+          <t>84350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>118640</t>
+          <t>130241</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>196847</t>
+          <t>214591</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106651; 147643</t>
+          <t>105697; 148259</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>105532; 147470</t>
+          <t>103740; 147975</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80455; 115657</t>
+          <t>81469; 114217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64752; 91070</t>
+          <t>70154; 99533</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>120727; 167906</t>
+          <t>122819; 166956</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>122600; 168402</t>
+          <t>121936; 167858</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>104163; 148881</t>
+          <t>104259; 148484</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>104420; 133261</t>
+          <t>113749; 146084</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>240609; 302019</t>
+          <t>242931; 304495</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>240791; 302872</t>
+          <t>240588; 306413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>194785; 252541</t>
+          <t>197069; 252663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>178091; 217600</t>
+          <t>192430; 236495</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>89980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>54265</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>131536</t>
+          <t>144246</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28066; 52579</t>
+          <t>29719; 54024</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33097; 60305</t>
+          <t>33859; 61966</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72787; 108290</t>
+          <t>70452; 108808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56437; 104717</t>
+          <t>75297; 109122</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17673; 39150</t>
+          <t>17484; 38489</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15024; 35161</t>
+          <t>14760; 35876</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35326; 65387</t>
+          <t>36146; 65330</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34167; 62431</t>
+          <t>43894; 68917</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51774; 83744</t>
+          <t>52305; 84497</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53820; 88510</t>
+          <t>54562; 87229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116520; 161571</t>
+          <t>115662; 162950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>99418; 154767</t>
+          <t>123302; 168328</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24959</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>44242</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6014; 20110</t>
+          <t>5473; 21207</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4010; 17259</t>
+          <t>4053; 16966</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10043; 29278</t>
+          <t>9858; 28544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17887; 34419</t>
+          <t>21552; 40247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3734; 15936</t>
+          <t>3495; 15571</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7421</t>
+          <t>0; 8084</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8523; 25240</t>
+          <t>8441; 24565</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8003; 19299</t>
+          <t>9784; 21526</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11557; 30269</t>
+          <t>10954; 29990</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5945; 21397</t>
+          <t>5316; 20423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21196; 45925</t>
+          <t>22148; 46521</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28817; 49712</t>
+          <t>34076; 56216</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>153538; 202598</t>
+          <t>153862; 202443</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>155833; 211960</t>
+          <t>153535; 209263</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176755; 230791</t>
+          <t>174682; 230081</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138207; 213386</t>
+          <t>179617; 231131</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>154493; 207824</t>
+          <t>155486; 205837</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>146360; 195298</t>
+          <t>145608; 195942</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>161238; 219881</t>
+          <t>163199; 220421</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>146409; 205395</t>
+          <t>178354; 221232</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>322063; 393925</t>
+          <t>319303; 393067</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>313504; 386567</t>
+          <t>314320; 387895</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>351132; 433055</t>
+          <t>352656; 433783</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>313296; 405725</t>
+          <t>371172; 437546</t>
         </is>
       </c>
     </row>
